--- a/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Easthill_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Easthill_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,14 +860,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Caramel Apple Butter</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monin - Caramel Apple Butter</t>
+          <t>Peanut Butter - Creamy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -877,12 +873,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -890,45 +886,49 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monin - Coconut</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>42.85</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Monin - Cookie Butter</t>
+          <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>79.83</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>79.83</t>
         </is>
       </c>
     </row>
@@ -936,91 +936,103 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Monin - Orange</t>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>6.96</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monin - Toffee Nut</t>
+          <t>Torani - Caramel Sauce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Monin - Vanilla Sugar Free</t>
+          <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WEB</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
+          <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>17.40</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>17.40</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1040,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Torani - White Chocolate Sauce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1038,12 +1050,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1055,57 +1067,61 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
+          <t>Whitefish Salad</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>77.97</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>155.94</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+          <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Web/EC</t>
+          <t>H&amp;M</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1115,51 +1131,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>11.94</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Web/EC</t>
+          <t>H&amp;M</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Wrap - Paper (6" x 10.75")</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.82</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WEB</t>
+          <t>Grandma's</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1169,12 +1185,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17.40</t>
+          <t>18.35</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1198,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>Bag Paper - Baguette</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1192,51 +1208,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.95</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Whitefish Salad</t>
+          <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>77.97</t>
+          <t>86.10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>155.94</t>
+          <t>258.30</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
+          <t>Copy Paper (8.5" x 11")</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1256,41 +1268,37 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>49.99</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>49.99</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>H&amp;M</t>
+          <t>Grandma's</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wrap - Paper (6" x 10.75")</t>
+          <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1300,12 +1308,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>18.35</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1325,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
+          <t>Grandma's Coffee Cake - Banana Walnut</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1331,156 +1339,6 @@
         </is>
       </c>
       <c r="E36" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Bag Paper - Baguette</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Kilogram Chai Concentrate</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>86.10</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>258.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Copy Paper (8.5" x 11")</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>49.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Grandma's</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Grandma's</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Grandma's Coffee Cake - Banana Walnut</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
         <is>
           <t>18.35</t>
         </is>
